--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B75810D-58FC-4C4C-9837-4400912033EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB933FDF7BE6D482929A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{777FC941-CC1D-4890-982B-D93975259493}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 09-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 14-09-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB933FDF7BE6D482929A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{777FC941-CC1D-4890-982B-D93975259493}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9338DFEB09D0A3329A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B33ED64E-01D6-47BC-8C02-F23C8418BA3A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9338DFEB09D0A3329A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B33ED64E-01D6-47BC-8C02-F23C8418BA3A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6BCA66-8426-4FB4-8563-AC4070A19F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6BCA66-8426-4FB4-8563-AC4070A19F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2575918E-D580-4A3A-8100-298B647F43F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 14-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 17-09-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -55,7 +55,7 @@
     <t>WinPLC _Privath__ (EG)</t>
   </si>
   <si>
-    <t>Xmedicus _Privath__ (Xmedicus Systems)</t>
+    <t>Xmedicus _Privath__ (XMedicus Systems)</t>
   </si>
   <si>
     <t>XMO _Privath__ (CGM)</t>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2575918E-D580-4A3A-8100-298B647F43F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B69159E-2E91-4615-BB3B-C5CF2B28B723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B69159E-2E91-4615-BB3B-C5CF2B28B723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D64DFF9F454B3D29A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{915A392B-F664-4BF5-BD57-55B737B01D7B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 17-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 18-09-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D64DFF9F454B3D29A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{915A392B-F664-4BF5-BD57-55B737B01D7B}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D66DFC9CD9CB2229A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D241CFE8-5C18-4B0F-910A-18861DCE76E8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 18-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 21-09-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D66DFC9CD9CB2229A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D241CFE8-5C18-4B0F-910A-18861DCE76E8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290A5D8E-926B-4BEB-BA44-013EDA344497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290A5D8E-926B-4BEB-BA44-013EDA344497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F666EB50-7B6E-48BA-B278-F14735E21161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 21-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 22-09-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F666EB50-7B6E-48BA-B278-F14735E21161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44EE0857-D36B-4199-BBB9-D8BF6A0947AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44EE0857-D36B-4199-BBB9-D8BF6A0947AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB4B68B-EDD2-423C-9A91-92E0B9128DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 22-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 23-09-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB4B68B-EDD2-423C-9A91-92E0B9128DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D6DD7881C9692629A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71D92E3F-5436-4734-A237-F9C88A6B00E8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D6DD7881C9692629A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71D92E3F-5436-4734-A237-F9C88A6B00E8}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9615537AD9BCA3B29A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A1A5229-BC9F-43D0-99D4-A004E5CBB5C4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 23-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 24-09-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -55,13 +55,13 @@
     <t>WinPLC _Privath__ (EG)</t>
   </si>
   <si>
-    <t>Xmedicus _Privath__ (XMedicus Systems)</t>
+    <t>XMedicus _Privath__ (XMedicus Systems)</t>
   </si>
   <si>
     <t>XMO _Privath__ (CGM)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9615537AD9BCA3B29A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A1A5229-BC9F-43D0-99D4-A004E5CBB5C4}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB961C530E5D7AB2A29A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7DA5B32-061C-4574-9D7E-32A1B790116B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB961C530E5D7AB2A29A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7DA5B32-061C-4574-9D7E-32A1B790116B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7E1FDC-67A5-418C-9937-F89960CEDE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 24-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 28-09-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7E1FDC-67A5-418C-9937-F89960CEDE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB96195B5D4E7CB3129A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DA64BE5-3369-4273-80A2-FC88EAE06894}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 28-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 02-10-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44EE0857-D36B-4199-BBB9-D8BF6A0947AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA7F4C3-5A23-4EF5-B2A6-C759883ACAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 22-09-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 07-10-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -55,13 +55,13 @@
     <t>WinPLC _Privath__ (EG)</t>
   </si>
   <si>
-    <t>Xmedicus _Privath__ (XMedicus Systems)</t>
+    <t>XMedicus _Privath__ (XMedicus Systems)</t>
   </si>
   <si>
     <t>XMO _Privath__ (CGM)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB96195B5D4E7CB3129A634B79670D86765" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DA64BE5-3369-4273-80A2-FC88EAE06894}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06330299-9F5A-43E7-A635-31898C7B0EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 02-10-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 07-10-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -629,9 +629,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -683,7 +683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -735,7 +735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -811,7 +811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -849,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -863,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -895,7 +895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -909,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -947,7 +947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>65</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>86</v>
       </c>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06330299-9F5A-43E7-A635-31898C7B0EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB96105BB864F8A2F29A634B79670D86761" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76FEF17E-41F6-4265-8D85-6FC574C3796C}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 07-10-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 08-10-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB96105BB864F8A2F29A634B79670D86761" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76FEF17E-41F6-4265-8D85-6FC574C3796C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A956E2D1-51DE-463A-85D4-14FD810DEB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 08-10-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 09-10-2026'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A956E2D1-51DE-463A-85D4-14FD810DEB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388FA390-2F54-4E32-9063-0854343294DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Privathospitalssystemer - sende_excel.XLSX
+++ b/html/Privathospitalssystemer - sende_excel.XLSX
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388FA390-2F54-4E32-9063-0854343294DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB94855B5E6B34922419E35BE7E71D87C5C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88CB61CE-4FDF-4B48-9F48-6E72B54EB9FE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 09-10-2026'!$A$1:$L$39</definedName>
+    <definedName name="Privathospitalssystemer___sende">'Opdateret d. 23-10-2026'!$A$1:$M$41</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="93">
   <si>
     <t>Standard</t>
   </si>
@@ -52,6 +52,9 @@
     <t>NOVAX _Privath__ (Novax)</t>
   </si>
   <si>
+    <t>Potensklinikken CRM (Potensklinikken)</t>
+  </si>
+  <si>
     <t>WinPLC _Privath__ (EG)</t>
   </si>
   <si>
@@ -121,6 +124,12 @@
     <t>DIS05 (D0533L)</t>
   </si>
   <si>
+    <t>Speciallægeepikrise</t>
+  </si>
+  <si>
+    <t>DIS07 (D0734L)</t>
+  </si>
+  <si>
     <t>Fysioterapiepikrise</t>
   </si>
   <si>
@@ -236,6 +245,12 @@
   </si>
   <si>
     <t>XDIS05 (XD0533L)</t>
+  </si>
+  <si>
+    <t>PrivateSpecialistLetter</t>
+  </si>
+  <si>
+    <t>XDIS07 (XD0734L)</t>
   </si>
   <si>
     <t>PhysiotherapiLetter</t>
@@ -628,10 +643,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -668,900 +683,961 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="s">
         <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="M12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>16</v>
       </c>
       <c r="J18" t="s">
-        <v>20</v>
-      </c>
-      <c r="K18" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="I19" t="s">
+        <v>21</v>
       </c>
       <c r="K19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="L19" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>52</v>
       </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" t="s">
-        <v>20</v>
-      </c>
-      <c r="I21" t="s">
-        <v>20</v>
-      </c>
-      <c r="K21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>53</v>
-      </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" t="s">
-        <v>20</v>
-      </c>
-      <c r="I23" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="E31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
-      </c>
-      <c r="K37" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>16</v>
+      </c>
+      <c r="L37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F38" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" t="s">
-        <v>25</v>
+        <v>15</v>
+      </c>
+      <c r="L39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
